--- a/ig/main/ValueSet-JDV-J286-ProfilUtilisateurReferentielNational-ROR.xlsx
+++ b/ig/main/ValueSet-JDV-J286-ProfilUtilisateurReferentielNational-ROR.xlsx
@@ -153,7 +153,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R369-ProfilUtilisateurReferentielNational/FHIR/TRE_R369-ProfilUtilisateurReferentielNational</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R369_ProfilUtilisateurReferentielNational/FHIR/TRE-R369-ProfilUtilisateurReferentielNational</t>
   </si>
 </sst>
 </file>

--- a/ig/main/ValueSet-JDV-J286-ProfilUtilisateurReferentielNational-ROR.xlsx
+++ b/ig/main/ValueSet-JDV-J286-ProfilUtilisateurReferentielNational-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
   <si>
     <t>Property</t>
   </si>
@@ -69,19 +69,7 @@
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>ANS (https://esante.gouv.fr)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>France</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Description</t>
@@ -287,7 +275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -384,36 +372,20 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" t="s" s="2">
-        <v>22</v>
-      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>24</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>23</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -432,82 +404,82 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-JDV-J286-ProfilUtilisateurReferentielNational-ROR.xlsx
+++ b/ig/main/ValueSet-JDV-J286-ProfilUtilisateurReferentielNational-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20241025120000</t>
+    <t>20241213120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T12:00:00+01:00</t>
+    <t>2024-12-13T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -133,6 +133,24 @@
   </si>
   <si>
     <t>Professionnel de Santé Libéral (PSL)</t>
+  </si>
+  <si>
+    <t>ADMIN_METIER</t>
+  </si>
+  <si>
+    <t>Administrateur Métier</t>
+  </si>
+  <si>
+    <t>SUPPORT</t>
+  </si>
+  <si>
+    <t>Support</t>
+  </si>
+  <si>
+    <t>REF_MSP</t>
+  </si>
+  <si>
+    <t>Référent Maison de Santé Pluriprofessionnelle</t>
   </si>
   <si>
     <t/>
@@ -395,7 +413,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -471,15 +489,39 @@
         <v>40</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-JDV-J286-ProfilUtilisateurReferentielNational-ROR.xlsx
+++ b/ig/main/ValueSet-JDV-J286-ProfilUtilisateurReferentielNational-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20241213120000</t>
+    <t>20250328120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-13T12:00:00+01:00</t>
+    <t>2025-03-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -151,6 +151,12 @@
   </si>
   <si>
     <t>Référent Maison de Santé Pluriprofessionnelle</t>
+  </si>
+  <si>
+    <t>REF_DISPO_PLACE</t>
+  </si>
+  <si>
+    <t>Référent saisie disponibilité en lit / place</t>
   </si>
   <si>
     <t/>
@@ -413,7 +419,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -513,15 +519,23 @@
         <v>46</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>48</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-JDV-J286-ProfilUtilisateurReferentielNational-ROR.xlsx
+++ b/ig/main/ValueSet-JDV-J286-ProfilUtilisateurReferentielNational-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
   <si>
     <t>Property</t>
   </si>
@@ -70,6 +70,12 @@
   </si>
   <si>
     <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -299,7 +305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -396,20 +402,28 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B14" t="s" s="2">
         <v>24</v>
+      </c>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -428,114 +442,114 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
